--- a/planilhasParaCruzamento/Fechamento Fev26 a Maio26 Vivo (1).xlsx
+++ b/planilhasParaCruzamento/Fechamento Fev26 a Maio26 Vivo (1).xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="7" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USERs\Documents\GitHub\pos-venda\planilhasParaCruzamento\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB728219-EFD3-431E-85B8-22B1EE2B0D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="684" yWindow="1104" windowWidth="23256" windowHeight="13176"/>
+    <workbookView minimized="1" xWindow="4740" yWindow="2580" windowWidth="22815" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FEVEREIRO26" sheetId="1" r:id="rId1"/>
@@ -14,20 +20,12 @@
     <sheet name="MAIO26 PF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main">
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -771,7 +769,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="000000000\-00"/>
@@ -1007,389 +1005,9 @@
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Separador de milhares" xfId="1" builtinId="3"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
-  <dxfs count="82">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="41">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1779,33 +1397,6 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <i val="0"/>
-        <color rgb="FFEE0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2146,37 +1737,38 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S45"/>
-  <sheetFormatPr defaultColWidth="10.90625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="10.88671875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="53.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="31.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.36328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.36328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="70" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="57.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="68.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4837,30 +4429,30 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="56.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7890,31 +7482,31 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:S78"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="69.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="69.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12522,31 +12114,31 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:S65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="74" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="30.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.1796875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.6328125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="30.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="24" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="27.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="24" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="69.1796875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="69.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="15.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16387,37 +15979,37 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:AA3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.26953125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37.26953125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="255.6328125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="25.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="255.6640625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="33.7265625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.77734375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="22.109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="33.77734375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -16671,82 +16263,82 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="81" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="41"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1:AA1">
-    <cfRule type="duplicateValues" dxfId="79" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="40"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="U2:U3">
-    <cfRule type="cellIs" dxfId="77" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="38" priority="39" operator="equal">
       <formula>"CANCELADO"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="75" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:A3">
-    <cfRule type="duplicateValues" dxfId="67" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="34"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z3">
-    <cfRule type="duplicateValues" dxfId="65" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="33"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z3">
-    <cfRule type="duplicateValues" dxfId="63" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z3">
-    <cfRule type="duplicateValues" dxfId="61" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="31"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:Z3">
-    <cfRule type="duplicateValues" dxfId="59" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AA3">
-    <cfRule type="duplicateValues" dxfId="57" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA3">
-    <cfRule type="duplicateValues" dxfId="55" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA3">
-    <cfRule type="duplicateValues" dxfId="53" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA3">
-    <cfRule type="duplicateValues" dxfId="51" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA2:AA3">
-    <cfRule type="duplicateValues" dxfId="49" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T3">
-    <cfRule type="duplicateValues" dxfId="47" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T2:T3">
-    <cfRule type="duplicateValues" dxfId="39" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="20"/>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U2:U3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"AGENDADO,AGUARDANDO ATIVAÇÃO,CANCELADO,EM ROTA,EXECUÇÃO,INSTALADO,MIGRAÇÃO NÃO REMUNERÁVEL,PEND. AGENDAMENTO,PEND. ENRIQUECIMENTO,PEND. RETENÇÃO,PEND. TÉCNICA,SERÁ CANCELADO,UPGRADE NÃO REMUNERÁVEL"</formula1>
     </dataValidation>
   </dataValidations>

--- a/planilhasParaCruzamento/Fechamento Fev26 a Maio26 Vivo (1).xlsx
+++ b/planilhasParaCruzamento/Fechamento Fev26 a Maio26 Vivo (1).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USERs\Documents\GitHub\pos-venda\planilhasParaCruzamento\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB728219-EFD3-431E-85B8-22B1EE2B0D0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{172A8024-073F-4D98-8CFA-A9C596E2DC01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="4740" yWindow="2580" windowWidth="22815" windowHeight="12375" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4170" yWindow="2340" windowWidth="22815" windowHeight="12375" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FEVEREIRO26" sheetId="1" r:id="rId1"/>
